--- a/resources/M626/ctq/spc_sheet_oos_detail.xlsx
+++ b/resources/M626/ctq/spc_sheet_oos_detail.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="20">
   <si>
     <t>factory</t>
   </si>
@@ -50,12 +50,39 @@
   </si>
   <si>
     <t>oos_type</t>
+  </si>
+  <si>
+    <t>ARRAY</t>
+  </si>
+  <si>
+    <t>M626</t>
+  </si>
+  <si>
+    <t>1K430</t>
+  </si>
+  <si>
+    <t>TPPOS_X_DIFF</t>
+  </si>
+  <si>
+    <t>L3MY6700305</t>
+  </si>
+  <si>
+    <t>L3MY6700315</t>
+  </si>
+  <si>
+    <t>L3MY6700330</t>
+  </si>
+  <si>
+    <t>LSL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -108,11 +135,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -407,7 +435,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -448,6 +476,120 @@
         <v>11</v>
       </c>
     </row>
+    <row r="2" spans="1:12">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="2">
+        <v>46229.215</v>
+      </c>
+      <c r="G2">
+        <v>-0.12</v>
+      </c>
+      <c r="H2">
+        <v>-21.36</v>
+      </c>
+      <c r="I2">
+        <v>-8.105984848484848</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>-1</v>
+      </c>
+      <c r="L2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="2">
+        <v>46229.28726851852</v>
+      </c>
+      <c r="G3">
+        <v>-0.45</v>
+      </c>
+      <c r="H3">
+        <v>-21.25</v>
+      </c>
+      <c r="I3">
+        <v>-8.102424242424242</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>-1</v>
+      </c>
+      <c r="L3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="2">
+        <v>46229.29991898148</v>
+      </c>
+      <c r="G4">
+        <v>-0.43</v>
+      </c>
+      <c r="H4">
+        <v>-21.4</v>
+      </c>
+      <c r="I4">
+        <v>-8.19439393939394</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>-1</v>
+      </c>
+      <c r="L4" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/resources/M626/ctq/spc_sheet_oos_detail.xlsx
+++ b/resources/M626/ctq/spc_sheet_oos_detail.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>factory</t>
   </si>
@@ -50,39 +50,12 @@
   </si>
   <si>
     <t>oos_type</t>
-  </si>
-  <si>
-    <t>ARRAY</t>
-  </si>
-  <si>
-    <t>M626</t>
-  </si>
-  <si>
-    <t>1K430</t>
-  </si>
-  <si>
-    <t>TPPOS_X_DIFF</t>
-  </si>
-  <si>
-    <t>L3MY6700305</t>
-  </si>
-  <si>
-    <t>L3MY6700315</t>
-  </si>
-  <si>
-    <t>L3MY6700330</t>
-  </si>
-  <si>
-    <t>LSL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -135,12 +108,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -435,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -476,120 +448,6 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" s="2">
-        <v>46229.215</v>
-      </c>
-      <c r="G2">
-        <v>-0.12</v>
-      </c>
-      <c r="H2">
-        <v>-21.36</v>
-      </c>
-      <c r="I2">
-        <v>-8.105984848484848</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>-1</v>
-      </c>
-      <c r="L2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="2">
-        <v>46229.28726851852</v>
-      </c>
-      <c r="G3">
-        <v>-0.45</v>
-      </c>
-      <c r="H3">
-        <v>-21.25</v>
-      </c>
-      <c r="I3">
-        <v>-8.102424242424242</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>-1</v>
-      </c>
-      <c r="L3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" s="2">
-        <v>46229.29991898148</v>
-      </c>
-      <c r="G4">
-        <v>-0.43</v>
-      </c>
-      <c r="H4">
-        <v>-21.4</v>
-      </c>
-      <c r="I4">
-        <v>-8.19439393939394</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>-1</v>
-      </c>
-      <c r="L4" t="s">
-        <v>19</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
